--- a/test.xlsx
+++ b/test.xlsx
@@ -1701,10 +1701,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E32"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelCol="4"/>
+  <dimension ref="A1:K32"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:11">
       <c r="A1">
         <v>500</v>
       </c>
@@ -1720,8 +1720,23 @@
       <c r="E1">
         <v>-4.1386</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="G1">
+        <v>250</v>
+      </c>
+      <c r="H1" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I1" s="1">
+        <v>0.892</v>
+      </c>
+      <c r="J1">
+        <v>-4.0103</v>
+      </c>
+      <c r="K1">
+        <v>-3.6864</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1737,8 +1752,23 @@
       <c r="E2">
         <v>-4.3588</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="G2">
+        <v>500</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I2" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="J2">
+        <v>-4.5968</v>
+      </c>
+      <c r="K2">
+        <v>-3.4793</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3">
         <v>1500</v>
       </c>
@@ -1754,8 +1784,23 @@
       <c r="E3">
         <v>-3.8401</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="G3">
+        <v>750</v>
+      </c>
+      <c r="H3" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="J3">
+        <v>-4.522</v>
+      </c>
+      <c r="K3">
+        <v>-3.4828</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -1771,8 +1816,23 @@
       <c r="E4">
         <v>-3.6625</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="G4">
+        <v>1000</v>
+      </c>
+      <c r="H4" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="J4">
+        <v>-4.5479</v>
+      </c>
+      <c r="K4">
+        <v>-3.4507</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5">
         <v>3000</v>
       </c>
@@ -1788,8 +1848,23 @@
       <c r="E5">
         <v>-3.7509</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="G5">
+        <v>1250</v>
+      </c>
+      <c r="H5" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I5" s="1">
+        <v>0.888</v>
+      </c>
+      <c r="J5">
+        <v>-4.3525</v>
+      </c>
+      <c r="K5">
+        <v>-3.6002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6">
         <v>4000</v>
       </c>
@@ -1805,8 +1880,23 @@
       <c r="E6">
         <v>-3.6682</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="G6">
+        <v>1500</v>
+      </c>
+      <c r="H6" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="I6" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="J6">
+        <v>-4.5285</v>
+      </c>
+      <c r="K6">
+        <v>-3.6174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7">
         <v>6000</v>
       </c>
@@ -1822,8 +1912,23 @@
       <c r="E7">
         <v>-3.5323</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="G7">
+        <v>1750</v>
+      </c>
+      <c r="H7" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="I7" s="1">
+        <v>0.888</v>
+      </c>
+      <c r="J7">
+        <v>-4.7974</v>
+      </c>
+      <c r="K7">
+        <v>-3.8947</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8">
         <v>7000</v>
       </c>
@@ -1839,8 +1944,23 @@
       <c r="E8">
         <v>-3.5302</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="G8">
+        <v>2000</v>
+      </c>
+      <c r="H8" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="I8" s="1">
+        <v>0.888</v>
+      </c>
+      <c r="J8">
+        <v>-4.8593</v>
+      </c>
+      <c r="K8">
+        <v>-3.9759</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9">
         <v>8000</v>
       </c>
@@ -1856,8 +1976,23 @@
       <c r="E9">
         <v>-3.5121</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="G9">
+        <v>2250</v>
+      </c>
+      <c r="H9" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I9" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J9">
+        <v>-4.1689</v>
+      </c>
+      <c r="K9">
+        <v>-3.5343</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10">
         <v>9000</v>
       </c>
@@ -1873,8 +2008,23 @@
       <c r="E10">
         <v>-3.37</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="G10">
+        <v>2500</v>
+      </c>
+      <c r="H10" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I10" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J10">
+        <v>-4.1805</v>
+      </c>
+      <c r="K10">
+        <v>-3.2213</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11">
         <v>10000</v>
       </c>
@@ -1890,8 +2040,23 @@
       <c r="E11">
         <v>-3.7679</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="G11">
+        <v>2750</v>
+      </c>
+      <c r="H11" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I11" s="1">
+        <v>0.912</v>
+      </c>
+      <c r="J11">
+        <v>-4.1264</v>
+      </c>
+      <c r="K11">
+        <v>-3.2124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
       <c r="A12">
         <v>11000</v>
       </c>
@@ -1907,8 +2072,23 @@
       <c r="E12">
         <v>-3.6248</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="G12">
+        <v>3000</v>
+      </c>
+      <c r="H12" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I12" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J12">
+        <v>-4.0249</v>
+      </c>
+      <c r="K12">
+        <v>-3.2884</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13">
         <v>12000</v>
       </c>
@@ -1924,8 +2104,23 @@
       <c r="E13">
         <v>-3.3219</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="G13">
+        <v>3250</v>
+      </c>
+      <c r="H13" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="I13" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J13">
+        <v>-4.0933</v>
+      </c>
+      <c r="K13">
+        <v>-3.4543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14">
         <v>13000</v>
       </c>
@@ -1941,8 +2136,23 @@
       <c r="E14">
         <v>-3.4445</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="G14">
+        <v>3500</v>
+      </c>
+      <c r="H14" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="I14" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J14">
+        <v>-4.091</v>
+      </c>
+      <c r="K14">
+        <v>-3.5854</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15">
         <v>13500</v>
       </c>
@@ -1958,8 +2168,23 @@
       <c r="E15">
         <v>-3.6318</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="G15">
+        <v>3750</v>
+      </c>
+      <c r="H15" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="I15" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J15">
+        <v>-4.1535</v>
+      </c>
+      <c r="K15">
+        <v>-3.5821</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16">
         <v>14000</v>
       </c>
@@ -1974,6 +2199,21 @@
       </c>
       <c r="E16">
         <v>-3.1938</v>
+      </c>
+      <c r="G16">
+        <v>4000</v>
+      </c>
+      <c r="H16" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="I16" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="J16">
+        <v>-4.2134</v>
+      </c>
+      <c r="K16">
+        <v>-3.5984</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -2389,8 +2629,8 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="5" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15" outlineLevelRow="6" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" s="1">
@@ -2465,6 +2705,9 @@
       <c r="D6">
         <v>-10.625</v>
       </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/test.xlsx
+++ b/test.xlsx
@@ -1701,10 +1701,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K32"/>
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:17">
       <c r="A1">
         <v>500</v>
       </c>
@@ -1735,8 +1735,23 @@
       <c r="K1">
         <v>-3.6864</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="M1">
+        <v>250</v>
+      </c>
+      <c r="N1" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="O1" s="1">
+        <v>0.912</v>
+      </c>
+      <c r="P1">
+        <v>-4.3833</v>
+      </c>
+      <c r="Q1">
+        <v>-3.3462</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1767,8 +1782,23 @@
       <c r="K2">
         <v>-3.4793</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>500</v>
+      </c>
+      <c r="N2" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="O2" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="P2">
+        <v>-4.1102</v>
+      </c>
+      <c r="Q2">
+        <v>-3.3407</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3">
         <v>1500</v>
       </c>
@@ -1799,8 +1829,23 @@
       <c r="K3">
         <v>-3.4828</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>750</v>
+      </c>
+      <c r="N3" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="O3" s="1">
+        <v>0.892</v>
+      </c>
+      <c r="P3">
+        <v>-4.1766</v>
+      </c>
+      <c r="Q3">
+        <v>-3.3397</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -1831,8 +1876,23 @@
       <c r="K4">
         <v>-3.4507</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>1000</v>
+      </c>
+      <c r="N4" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="O4" s="1">
+        <v>0.912</v>
+      </c>
+      <c r="P4">
+        <v>-4.1182</v>
+      </c>
+      <c r="Q4">
+        <v>-3.3339</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5">
         <v>3000</v>
       </c>
@@ -1863,8 +1923,23 @@
       <c r="K5">
         <v>-3.6002</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>1250</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="O5" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="P5">
+        <v>-4.5955</v>
+      </c>
+      <c r="Q5">
+        <v>-3.5169</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17">
       <c r="A6">
         <v>4000</v>
       </c>
@@ -1895,8 +1970,23 @@
       <c r="K6">
         <v>-3.6174</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>1500</v>
+      </c>
+      <c r="N6" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="O6" s="1">
+        <v>0.888</v>
+      </c>
+      <c r="P6">
+        <v>-4.2559</v>
+      </c>
+      <c r="Q6">
+        <v>-3.6748</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7">
         <v>6000</v>
       </c>
@@ -1927,8 +2017,23 @@
       <c r="K7">
         <v>-3.8947</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>1750</v>
+      </c>
+      <c r="N7" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="O7" s="1">
+        <v>0.888</v>
+      </c>
+      <c r="P7">
+        <v>-4.6736</v>
+      </c>
+      <c r="Q7">
+        <v>-3.8438</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8">
         <v>7000</v>
       </c>
@@ -1959,8 +2064,23 @@
       <c r="K8">
         <v>-3.9759</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>2000</v>
+      </c>
+      <c r="N8" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="O8" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="P8">
+        <v>-4.7518</v>
+      </c>
+      <c r="Q8">
+        <v>-3.7646</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9">
         <v>8000</v>
       </c>
@@ -1991,8 +2111,23 @@
       <c r="K9">
         <v>-3.5343</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9">
+        <v>2250</v>
+      </c>
+      <c r="N9" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="O9" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="P9">
+        <v>-4.246</v>
+      </c>
+      <c r="Q9">
+        <v>-3.5466</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10">
         <v>9000</v>
       </c>
@@ -2023,8 +2158,23 @@
       <c r="K10">
         <v>-3.2213</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>2500</v>
+      </c>
+      <c r="N10" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="O10" s="1">
+        <v>0.908</v>
+      </c>
+      <c r="P10">
+        <v>-4.2679</v>
+      </c>
+      <c r="Q10">
+        <v>-3.5801</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11">
         <v>10000</v>
       </c>
@@ -2056,7 +2206,7 @@
         <v>-3.2124</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:17">
       <c r="A12">
         <v>11000</v>
       </c>
@@ -2088,7 +2238,7 @@
         <v>-3.2884</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:17">
       <c r="A13">
         <v>12000</v>
       </c>
@@ -2120,7 +2270,7 @@
         <v>-3.4543</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:17">
       <c r="A14">
         <v>13000</v>
       </c>
@@ -2152,7 +2302,7 @@
         <v>-3.5854</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:17">
       <c r="A15">
         <v>13500</v>
       </c>
@@ -2184,7 +2334,7 @@
         <v>-3.5821</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:17">
       <c r="A16">
         <v>14000</v>
       </c>

--- a/test.xlsx
+++ b/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11700" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="11100" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
   <si>
     <t>post cutoff percent</t>
   </si>
@@ -55,6 +55,9 @@
   </si>
   <si>
     <t>Fail</t>
+  </si>
+  <si>
+    <t>Failed</t>
   </si>
 </sst>
 </file>
@@ -1701,10 +1704,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q32"/>
+  <dimension ref="A1:V48"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:22">
       <c r="A1">
         <v>500</v>
       </c>
@@ -1750,8 +1753,20 @@
       <c r="Q1">
         <v>-3.3462</v>
       </c>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="S1" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="T1" s="1">
+        <v>0.842</v>
+      </c>
+      <c r="U1">
+        <v>-4.7936</v>
+      </c>
+      <c r="V1">
+        <v>-4.0455</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>1000</v>
       </c>
@@ -1797,8 +1812,20 @@
       <c r="Q2">
         <v>-3.3407</v>
       </c>
-    </row>
-    <row r="3" spans="1:17">
+      <c r="S2" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.862</v>
+      </c>
+      <c r="U2">
+        <v>-4.7428</v>
+      </c>
+      <c r="V2">
+        <v>-4.5375</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>1500</v>
       </c>
@@ -1844,8 +1871,20 @@
       <c r="Q3">
         <v>-3.3397</v>
       </c>
-    </row>
-    <row r="4" spans="1:17">
+      <c r="S3" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U3">
+        <v>-5.2592</v>
+      </c>
+      <c r="V3">
+        <v>-4.2156</v>
+      </c>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>2000</v>
       </c>
@@ -1861,6 +1900,9 @@
       <c r="E4">
         <v>-3.6625</v>
       </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
       <c r="G4">
         <v>1000</v>
       </c>
@@ -1891,8 +1933,23 @@
       <c r="Q4">
         <v>-3.3339</v>
       </c>
-    </row>
-    <row r="5" spans="1:17">
+      <c r="R4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U4">
+        <v>-4.879</v>
+      </c>
+      <c r="V4">
+        <v>-4.2565</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>3000</v>
       </c>
@@ -1938,8 +1995,20 @@
       <c r="Q5">
         <v>-3.5169</v>
       </c>
-    </row>
-    <row r="6" spans="1:17">
+      <c r="S5" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="U5">
+        <v>-5.2771</v>
+      </c>
+      <c r="V5">
+        <v>-4.4095</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>4000</v>
       </c>
@@ -1985,8 +2054,20 @@
       <c r="Q6">
         <v>-3.6748</v>
       </c>
-    </row>
-    <row r="7" spans="1:17">
+      <c r="S6" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U6">
+        <v>-4.7428</v>
+      </c>
+      <c r="V6">
+        <v>-3.9351</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>6000</v>
       </c>
@@ -2032,8 +2113,20 @@
       <c r="Q7">
         <v>-3.8438</v>
       </c>
-    </row>
-    <row r="8" spans="1:17">
+      <c r="S7" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U7">
+        <v>-4.692</v>
+      </c>
+      <c r="V7">
+        <v>-3.8405</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>7000</v>
       </c>
@@ -2079,8 +2172,20 @@
       <c r="Q8">
         <v>-3.7646</v>
       </c>
-    </row>
-    <row r="9" spans="1:17">
+      <c r="S8" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U8">
+        <v>-4.6516</v>
+      </c>
+      <c r="V8">
+        <v>-3.7771</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>8000</v>
       </c>
@@ -2126,8 +2231,20 @@
       <c r="Q9">
         <v>-3.5466</v>
       </c>
-    </row>
-    <row r="10" spans="1:17">
+      <c r="S9" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="U9">
+        <v>-4.4302</v>
+      </c>
+      <c r="V9">
+        <v>-4.1077</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>9000</v>
       </c>
@@ -2173,8 +2290,23 @@
       <c r="Q10">
         <v>-3.5801</v>
       </c>
-    </row>
-    <row r="11" spans="1:17">
+      <c r="R10" t="s">
+        <v>8</v>
+      </c>
+      <c r="S10" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T10" s="1">
+        <v>0.846</v>
+      </c>
+      <c r="U10">
+        <v>-4.485</v>
+      </c>
+      <c r="V10">
+        <v>-4.1297</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>10000</v>
       </c>
@@ -2205,8 +2337,11 @@
       <c r="K11">
         <v>-3.2124</v>
       </c>
-    </row>
-    <row r="12" spans="1:17">
+      <c r="L11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>11000</v>
       </c>
@@ -2237,8 +2372,20 @@
       <c r="K12">
         <v>-3.2884</v>
       </c>
-    </row>
-    <row r="13" spans="1:17">
+      <c r="S12" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="T12" s="1">
+        <v>0.846</v>
+      </c>
+      <c r="U12">
+        <v>-4.7624</v>
+      </c>
+      <c r="V12">
+        <v>-4.0544</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22">
       <c r="A13">
         <v>12000</v>
       </c>
@@ -2269,8 +2416,20 @@
       <c r="K13">
         <v>-3.4543</v>
       </c>
-    </row>
-    <row r="14" spans="1:17">
+      <c r="S13" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="T13" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="U13">
+        <v>-4.7893</v>
+      </c>
+      <c r="V13">
+        <v>-4.4098</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22">
       <c r="A14">
         <v>13000</v>
       </c>
@@ -2301,8 +2460,20 @@
       <c r="K14">
         <v>-3.5854</v>
       </c>
-    </row>
-    <row r="15" spans="1:17">
+      <c r="S14" s="1">
+        <v>0.8</v>
+      </c>
+      <c r="T14" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U14">
+        <v>-5.4081</v>
+      </c>
+      <c r="V14">
+        <v>-4.1591</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22">
       <c r="A15">
         <v>13500</v>
       </c>
@@ -2333,8 +2504,20 @@
       <c r="K15">
         <v>-3.5821</v>
       </c>
-    </row>
-    <row r="16" spans="1:17">
+      <c r="S15" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="T15" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U15">
+        <v>-4.9304</v>
+      </c>
+      <c r="V15">
+        <v>-4.0485</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22">
       <c r="A16">
         <v>14000</v>
       </c>
@@ -2365,8 +2548,20 @@
       <c r="K16">
         <v>-3.5984</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="S16" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="T16" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="U16">
+        <v>-5.4017</v>
+      </c>
+      <c r="V16">
+        <v>-4.2931</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17">
         <v>14500</v>
       </c>
@@ -2383,7 +2578,7 @@
         <v>-3.2628</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:6">
       <c r="A18">
         <v>15000</v>
       </c>
@@ -2399,8 +2594,11 @@
       <c r="E18">
         <v>-3.1142</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19">
         <v>15500</v>
       </c>
@@ -2417,7 +2615,7 @@
         <v>-3.4335</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20">
         <v>16000</v>
       </c>
@@ -2434,7 +2632,7 @@
         <v>-3.2149</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:6">
       <c r="A21">
         <v>16500</v>
       </c>
@@ -2451,7 +2649,7 @@
         <v>-3.2053</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:6">
       <c r="A22">
         <v>17000</v>
       </c>
@@ -2468,7 +2666,7 @@
         <v>-3.1278</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23">
         <v>18000</v>
       </c>
@@ -2485,7 +2683,7 @@
         <v>-3.301</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:6">
       <c r="A24">
         <v>19000</v>
       </c>
@@ -2502,7 +2700,7 @@
         <v>-3.3493</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:6">
       <c r="A25">
         <v>20000</v>
       </c>
@@ -2519,7 +2717,7 @@
         <v>-3.4038</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26">
         <v>21000</v>
       </c>
@@ -2536,7 +2734,7 @@
         <v>-3.1642</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:6">
       <c r="A27">
         <v>22000</v>
       </c>
@@ -2553,7 +2751,7 @@
         <v>-3.383</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:6">
       <c r="A28">
         <v>23000</v>
       </c>
@@ -2570,7 +2768,7 @@
         <v>-3.3911</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:6">
       <c r="A29">
         <v>23500</v>
       </c>
@@ -2587,7 +2785,7 @@
         <v>-3.3005</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:6">
       <c r="A30">
         <v>24000</v>
       </c>
@@ -2604,7 +2802,7 @@
         <v>-3.3393</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="A31">
         <v>24500</v>
       </c>
@@ -2621,7 +2819,7 @@
         <v>-3.2952</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:6">
       <c r="A32">
         <v>25000</v>
       </c>
@@ -2636,6 +2834,264 @@
       </c>
       <c r="E32">
         <v>-3.3127</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
+      <c r="A34">
+        <v>500</v>
+      </c>
+      <c r="B34" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="C34" s="1">
+        <v>0.842</v>
+      </c>
+      <c r="D34">
+        <v>-3.9875</v>
+      </c>
+      <c r="E34">
+        <v>-3.4485</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
+      <c r="A35">
+        <v>1000</v>
+      </c>
+      <c r="B35" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="C35" s="1">
+        <v>0.842</v>
+      </c>
+      <c r="D35">
+        <v>-3.879</v>
+      </c>
+      <c r="E35">
+        <v>-3.2653</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
+      <c r="A36">
+        <v>1500</v>
+      </c>
+      <c r="B36" s="1">
+        <v>0.775</v>
+      </c>
+      <c r="C36" s="1">
+        <v>0.779</v>
+      </c>
+      <c r="D36">
+        <v>-5.2199</v>
+      </c>
+      <c r="E36">
+        <v>-4.0459</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
+      <c r="A37">
+        <v>2000</v>
+      </c>
+      <c r="B37" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C37" s="1">
+        <v>0.862</v>
+      </c>
+      <c r="D37">
+        <v>-4.1023</v>
+      </c>
+      <c r="E37">
+        <v>-3.1564</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
+      <c r="A38">
+        <v>2500</v>
+      </c>
+      <c r="B38" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C38" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="D38">
+        <v>-4.2394</v>
+      </c>
+      <c r="E38">
+        <v>-3.2646</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
+      <c r="A39">
+        <v>3000</v>
+      </c>
+      <c r="B39" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="C39" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="D39">
+        <v>-4.0006</v>
+      </c>
+      <c r="E39">
+        <v>-3.1669</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
+      <c r="A40">
+        <v>3500</v>
+      </c>
+      <c r="B40" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C40" s="1">
+        <v>0.912</v>
+      </c>
+      <c r="D40">
+        <v>-4.2678</v>
+      </c>
+      <c r="E40">
+        <v>-3.4589</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
+      <c r="A41">
+        <v>4000</v>
+      </c>
+      <c r="B41" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C41" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="D41">
+        <v>-4.1638</v>
+      </c>
+      <c r="E41">
+        <v>-3.5089</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
+      <c r="A42">
+        <v>4500</v>
+      </c>
+      <c r="B42" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C42" s="1">
+        <v>0.883</v>
+      </c>
+      <c r="D42">
+        <v>-4.4063</v>
+      </c>
+      <c r="E42">
+        <v>-3.2075</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="A43">
+        <v>5000</v>
+      </c>
+      <c r="B43" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C43" s="1">
+        <v>0.883</v>
+      </c>
+      <c r="D43">
+        <v>-4.0624</v>
+      </c>
+      <c r="E43">
+        <v>-2.8082</v>
+      </c>
+      <c r="F43" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="A44">
+        <v>5500</v>
+      </c>
+      <c r="B44" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C44" s="1">
+        <v>0.867</v>
+      </c>
+      <c r="D44">
+        <v>-4.4472</v>
+      </c>
+      <c r="E44">
+        <v>-3.3054</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="A45">
+        <v>6000</v>
+      </c>
+      <c r="B45" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C45" s="1">
+        <v>0.871</v>
+      </c>
+      <c r="D45">
+        <v>-4.4364</v>
+      </c>
+      <c r="E45">
+        <v>-3.3343</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="A46">
+        <v>6500</v>
+      </c>
+      <c r="B46" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C46" s="1">
+        <v>0.846</v>
+      </c>
+      <c r="D46">
+        <v>-4.6176</v>
+      </c>
+      <c r="E46">
+        <v>-3.664</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="A47">
+        <v>7000</v>
+      </c>
+      <c r="B47" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C47" s="1">
+        <v>0.842</v>
+      </c>
+      <c r="D47">
+        <v>-5.4199</v>
+      </c>
+      <c r="E47">
+        <v>-3.628</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
+      <c r="A48">
+        <v>7500</v>
+      </c>
+      <c r="B48" s="1">
+        <v>0.85</v>
+      </c>
+      <c r="C48" s="1">
+        <v>0.892</v>
+      </c>
+      <c r="D48">
+        <v>-4.4325</v>
+      </c>
+      <c r="E48">
+        <v>-3.3756</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11100" activeTab="2"/>
+    <workbookView windowWidth="14010" windowHeight="5580" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="10">
   <si>
     <t>post cutoff percent</t>
   </si>
@@ -58,6 +58,9 @@
   </si>
   <si>
     <t>Failed</t>
+  </si>
+  <si>
+    <t>2024 year</t>
   </si>
 </sst>
 </file>
@@ -1704,7 +1707,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V48"/>
+  <dimension ref="A1:V55"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:22">
@@ -3092,6 +3095,108 @@
       </c>
       <c r="E48">
         <v>-3.3756</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
+      <c r="A50" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
+      <c r="A51">
+        <v>1500</v>
+      </c>
+      <c r="B51" s="1">
+        <v>0.375</v>
+      </c>
+      <c r="C51" s="1">
+        <v>0.588</v>
+      </c>
+      <c r="D51">
+        <v>-12.2562</v>
+      </c>
+      <c r="E51">
+        <v>-11.2603</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
+      <c r="A52">
+        <v>3000</v>
+      </c>
+      <c r="B52" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="C52" s="1">
+        <v>0.642</v>
+      </c>
+      <c r="D52">
+        <v>-9.6948</v>
+      </c>
+      <c r="E52">
+        <v>-10.2921</v>
+      </c>
+      <c r="F52" s="1">
+        <v>0.914</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
+      <c r="A53">
+        <v>4500</v>
+      </c>
+      <c r="B53" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="C53" s="1">
+        <v>0.733</v>
+      </c>
+      <c r="D53">
+        <v>-9.7527</v>
+      </c>
+      <c r="E53">
+        <v>-8.3458</v>
+      </c>
+      <c r="F53" s="1">
+        <v>0.8109</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
+      <c r="A54">
+        <v>6000</v>
+      </c>
+      <c r="B54" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="C54" s="1">
+        <v>0.721</v>
+      </c>
+      <c r="D54">
+        <v>-8.8214</v>
+      </c>
+      <c r="E54">
+        <v>-7.1411</v>
+      </c>
+      <c r="F54" s="1">
+        <v>0.8556</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
+      <c r="A55">
+        <v>7500</v>
+      </c>
+      <c r="B55" s="1">
+        <v>0.825</v>
+      </c>
+      <c r="C55" s="1">
+        <v>0.783</v>
+      </c>
+      <c r="D55">
+        <v>-7.7781</v>
+      </c>
+      <c r="E55">
+        <v>-6.6901</v>
+      </c>
+      <c r="F55" s="1">
+        <v>0.9368</v>
       </c>
     </row>
   </sheetData>

--- a/test.xlsx
+++ b/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14010" windowHeight="5580" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="11100" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="11">
   <si>
     <t>post cutoff percent</t>
   </si>
@@ -61,6 +61,9 @@
   </si>
   <si>
     <t>2024 year</t>
+  </si>
+  <si>
+    <t>cpt:0.8, fineweb:0.2</t>
   </si>
 </sst>
 </file>
@@ -3097,12 +3100,15 @@
         <v>-3.3756</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:12">
       <c r="A50" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="51" spans="1:6">
+      <c r="I50" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12">
       <c r="A51">
         <v>1500</v>
       </c>
@@ -3118,8 +3124,23 @@
       <c r="E51">
         <v>-11.2603</v>
       </c>
-    </row>
-    <row r="52" spans="1:6">
+      <c r="H51">
+        <v>1000</v>
+      </c>
+      <c r="I51" s="1">
+        <v>0.475</v>
+      </c>
+      <c r="J51" s="1">
+        <v>0.637</v>
+      </c>
+      <c r="K51">
+        <v>-11.7114</v>
+      </c>
+      <c r="L51">
+        <v>-10.6389</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12">
       <c r="A52">
         <v>3000</v>
       </c>
@@ -3138,8 +3159,20 @@
       <c r="F52" s="1">
         <v>0.914</v>
       </c>
-    </row>
-    <row r="53" spans="1:6">
+      <c r="I52" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="J52" s="1">
+        <v>0.667</v>
+      </c>
+      <c r="K52">
+        <v>-9.6284</v>
+      </c>
+      <c r="L52">
+        <v>-9.2401</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12">
       <c r="A53">
         <v>4500</v>
       </c>
@@ -3159,7 +3192,7 @@
         <v>0.8109</v>
       </c>
     </row>
-    <row r="54" spans="1:6">
+    <row r="54" spans="1:12">
       <c r="A54">
         <v>6000</v>
       </c>
@@ -3179,7 +3212,7 @@
         <v>0.8556</v>
       </c>
     </row>
-    <row r="55" spans="1:6">
+    <row r="55" spans="1:12">
       <c r="A55">
         <v>7500</v>
       </c>

--- a/test.xlsx
+++ b/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11100" activeTab="2"/>
+    <workbookView windowWidth="28800" windowHeight="11700" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="2021" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="12">
   <si>
     <t>post cutoff percent</t>
   </si>
@@ -64,6 +64,9 @@
   </si>
   <si>
     <t>cpt:0.8, fineweb:0.2</t>
+  </si>
+  <si>
+    <t>cpt: 0.95, category : 0.05</t>
   </si>
 </sst>
 </file>
@@ -3100,15 +3103,18 @@
         <v>-3.3756</v>
       </c>
     </row>
-    <row r="50" spans="1:12">
+    <row r="50" spans="1:18">
       <c r="A50" t="s">
         <v>9</v>
       </c>
       <c r="I50" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="51" spans="1:12">
+      <c r="N50" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18">
       <c r="A51">
         <v>1500</v>
       </c>
@@ -3139,8 +3145,23 @@
       <c r="L51">
         <v>-10.6389</v>
       </c>
-    </row>
-    <row r="52" spans="1:12">
+      <c r="N51">
+        <v>1000</v>
+      </c>
+      <c r="O51" s="1">
+        <v>0.5</v>
+      </c>
+      <c r="P51" s="1">
+        <v>0.642</v>
+      </c>
+      <c r="Q51">
+        <v>-11.2652</v>
+      </c>
+      <c r="R51">
+        <v>-9.9791</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18">
       <c r="A52">
         <v>3000</v>
       </c>
@@ -3159,6 +3180,9 @@
       <c r="F52" s="1">
         <v>0.914</v>
       </c>
+      <c r="H52">
+        <v>2000</v>
+      </c>
       <c r="I52" s="1">
         <v>0.625</v>
       </c>
@@ -3171,8 +3195,23 @@
       <c r="L52">
         <v>-9.2401</v>
       </c>
-    </row>
-    <row r="53" spans="1:12">
+      <c r="N52">
+        <v>2000</v>
+      </c>
+      <c r="O52" s="1">
+        <v>0.6</v>
+      </c>
+      <c r="P52" s="1">
+        <v>0.675</v>
+      </c>
+      <c r="Q52">
+        <v>-10.2443</v>
+      </c>
+      <c r="R52">
+        <v>-9.8982</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18">
       <c r="A53">
         <v>4500</v>
       </c>
@@ -3191,8 +3230,23 @@
       <c r="F53" s="1">
         <v>0.8109</v>
       </c>
-    </row>
-    <row r="54" spans="1:12">
+      <c r="N53">
+        <v>3000</v>
+      </c>
+      <c r="O53" s="1">
+        <v>0.625</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0.721</v>
+      </c>
+      <c r="Q53">
+        <v>-10.1317</v>
+      </c>
+      <c r="R53">
+        <v>-9.0458</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18">
       <c r="A54">
         <v>6000</v>
       </c>
@@ -3211,8 +3265,23 @@
       <c r="F54" s="1">
         <v>0.8556</v>
       </c>
-    </row>
-    <row r="55" spans="1:12">
+      <c r="N54">
+        <v>4000</v>
+      </c>
+      <c r="O54" s="1">
+        <v>0.65</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0.767</v>
+      </c>
+      <c r="Q54">
+        <v>-9.8482</v>
+      </c>
+      <c r="R54">
+        <v>-8.7919</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18">
       <c r="A55">
         <v>7500</v>
       </c>
